--- a/punmicro/templates/writing/U04.xlsx
+++ b/punmicro/templates/writing/U04.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="内容编写" sheetId="1" r:id="R004a5270851e4274"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图片与视频" sheetId="2" r:id="R0ecaad5c0ae2483e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEO与Schema" sheetId="3" r:id="R6e55c0c5ef414fd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发检查" sheetId="4" r:id="R98abf2b8ffd84e51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="内容编写" sheetId="1" r:id="R8a146c8f801f4bcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图片与视频" sheetId="2" r:id="R3a4a11d91ca24d60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEO与Schema" sheetId="3" r:id="R55450a90b4c64c5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发检查" sheetId="4" r:id="Rfc897fe7f46c4a76"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="17">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -136,6 +136,9 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -397,7 +400,7 @@
       </x:c>
       <x:c r="B3" s="3"/>
       <x:c r="C3" s="3" t="str">
-        <x:v>pun-IPAN Anaerobic Workstations</x:v>
+        <x:v>pun-IPAN Anaerobic and Hypoxic Workstations</x:v>
       </x:c>
       <x:c r="D3" s="3" t="str">
         <x:v>有效规划模板，资料齐备后进入开发</x:v>
@@ -518,7 +521,7 @@
         <x:v>需要提供的资料</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="74" customHeight="1">
+    <x:row r="8" ht="164" customHeight="1">
       <x:c r="A8" s="11" t="str">
         <x:v>U04-001</x:v>
       </x:c>
@@ -526,20 +529,23 @@
         <x:v>H1</x:v>
       </x:c>
       <x:c r="C8" s="12" t="str">
-        <x:v>pun-IPAN Anaerobic Workstations</x:v>
+        <x:v>pun-IPAN Anaerobic and Hypoxic Workstations</x:v>
       </x:c>
       <x:c r="D8" s="12" t="str">
-        <x:v>pun-IPAN 厌氧工作站</x:v>
+        <x:v>pun-IPAN 厌氧与低氧工作站</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str">
-        <x:v>说明已确认的厌氧工作空间任务及适用范围，不使用低氧H55资料或外推氧控制性能。</x:v>
+        <x:v>开头区分厌氧与低氧两个版本，说明低氧版的微需氧微生物操作培养、细胞与组织低氧培养任务；配置与参数引用对应型号资料。</x:v>
       </x:c>
       <x:c r="F8" s="11" t="str">
         <x:v>The Whitley A95 provides an anaerobic workspace with four oval access ports, allowing two operators to work in the same chamber.
-https://www.dwscientific.com/whitley-anaerobic-workstations/whitley-a95-workstation</x:v>
+https://www.dwscientific.com/whitley-anaerobic-workstations/whitley-a95-workstation
+The Whitley H55 provides a low-oxygen workspace for cell and tissue culture, with controls for oxygen, carbon dioxide and humidity. Researchers can work with cultures inside the controlled chamber environment.
+https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>Whitley A95提供配有四个椭圆操作口的厌氧工作空间，可让两名操作人员在同一腔体中工作。</x:v>
+        <x:v>Whitley A95提供配有四个椭圆操作口的厌氧工作空间，可让两名操作人员在同一腔体中工作。
+Whitley H55为细胞与组织培养提供低氧工作空间，可控制氧气、二氧化碳和湿度。研究人员可在腔体内的受控环境中操作培养物。</x:v>
       </x:c>
       <x:c r="H8" s="13" t="str"/>
       <x:c r="I8" s="13" t="str"/>
@@ -548,16 +554,16 @@
         <x:v>待填写</x:v>
       </x:c>
       <x:c r="L8" s="3" t="str">
-        <x:v>pun-IPAN 厌氧工作站</x:v>
+        <x:v>pun-IPAN 厌氧与低氧工作站</x:v>
       </x:c>
       <x:c r="M8" s="3" t="str">
         <x:v>操作口与使用人数让工作空间更具体。PUN先说明需要在腔体内完成的实验任务。</x:v>
       </x:c>
       <x:c r="N8" s="3" t="str">
-        <x:v>pun-IPAN已确认的任务、工作环境及观察操作说明。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="74" customHeight="1">
+        <x:v>厌氧与低氧版本产品资料；低氧版微需氧微生物、细胞与组织两类任务说明及对应型号。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="164" customHeight="1">
       <x:c r="A9" s="11" t="str">
         <x:v>U04-002</x:v>
       </x:c>
@@ -565,20 +571,23 @@
         <x:v>H2</x:v>
       </x:c>
       <x:c r="C9" s="12" t="str">
-        <x:v>Anaerobic Handling Tasks and Workspace Planning</x:v>
+        <x:v>Choose the Anaerobic or Hypoxic Version</x:v>
       </x:c>
       <x:c r="D9" s="12" t="str">
-        <x:v>厌氧操作任务与工作空间规划</x:v>
+        <x:v>选择厌氧或低氧版本</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str">
-        <x:v>从材料处理、观察和培养任务解释空间需求；不先堆无来源容量数值。</x:v>
+        <x:v>用任务对照表帮助选择：厌氧任务、微需氧微生物操作培养、细胞与组织低氧培养，分别列对应版本及使用条件。</x:v>
       </x:c>
       <x:c r="F9" s="11" t="str">
         <x:v>The stated capacity is 960–1,120 plates of 90 mm, depending on configuration. Capacity needs to be read with loading and option details.
-https://www.dwscientific.com/whitley-anaerobic-workstations/whitley-a95-workstation</x:v>
+https://www.dwscientific.com/whitley-anaerobic-workstations/whitley-a95-workstation
+The Whitley H55 provides a low-oxygen workspace for cell and tissue culture, with controls for oxygen, carbon dioxide and humidity. Researchers can work with cultures inside the controlled chamber environment.
+https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>页面标示可放置960–1,120块90毫米平板，具体取决于配置；容量需结合装载方式和选项理解。</x:v>
+        <x:v>页面标示可放置960–1,120块90毫米平板，具体取决于配置；容量需结合装载方式和选项理解。
+Whitley H55为细胞与组织培养提供低氧工作空间，可控制氧气、二氧化碳和湿度。研究人员可在腔体内的受控环境中操作培养物。</x:v>
       </x:c>
       <x:c r="H9" s="13" t="str"/>
       <x:c r="I9" s="13" t="str"/>
@@ -587,16 +596,16 @@
         <x:v>待填写</x:v>
       </x:c>
       <x:c r="L9" s="3" t="str">
-        <x:v>厌氧操作任务与工作空间规划</x:v>
+        <x:v>选择厌氧或低氧版本</x:v>
       </x:c>
       <x:c r="M9" s="3" t="str">
-        <x:v>容量以范围表示，提示配置会影响装载。PUN同时展示板架、工作区和实际操作空间。</x:v>
+        <x:v>H55的任务、配置和选项分散在不同栏目。PUN用版本选择表将任务、使用条件、标准配置、选配和对应资料放在一起。</x:v>
       </x:c>
       <x:c r="N9" s="3" t="str">
-        <x:v>pun-IPAN已确认的任务、工作环境及观察操作说明。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="74" customHeight="1">
+        <x:v>任务、版本和配置对照表，注明对应型号、适用样本与使用条件。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="164" customHeight="1">
       <x:c r="A10" s="3" t="str">
         <x:v>U04-003</x:v>
       </x:c>
@@ -604,20 +613,23 @@
         <x:v>H3</x:v>
       </x:c>
       <x:c r="C10" s="3" t="str">
-        <x:v>Manipulation, Observation and Culture Tasks</x:v>
+        <x:v>Microbial Handling and Cell or Tissue Culture Tasks</x:v>
       </x:c>
       <x:c r="D10" s="3" t="str">
-        <x:v>操作、观察与培养任务</x:v>
+        <x:v>微生物操作与细胞或组织培养任务</x:v>
       </x:c>
       <x:c r="E10" s="3" t="str">
-        <x:v>按PUN已确认的资料逐项确认任务与边界，不把DWS功能表改品牌。</x:v>
+        <x:v>分别说明低氧版的两类任务，列输入材料、人员操作和过程记录；厌氧任务单列对应版本与适用资料。</x:v>
       </x:c>
       <x:c r="F10" s="3" t="str">
-        <x:v>An optional divider and sliding door create two temperature zones; a three-gas variant uses nitrogen, hydrogen and carbon dioxide.
+        <x:v>The Whitley H55 provides a low-oxygen workspace for cell and tissue culture, with controls for oxygen, carbon dioxide and humidity. Researchers can work with cultures inside the controlled chamber environment.
+https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation
+An optional divider and sliding door create two temperature zones; a three-gas variant uses nitrogen, hydrogen and carbon dioxide.
 https://www.dwscientific.com/whitley-anaerobic-workstations/whitley-a55-workstation</x:v>
       </x:c>
       <x:c r="G10" s="3" t="str">
-        <x:v>可选隔板与滑门形成两个温区；三气版本使用氮气、氢气和二氧化碳。</x:v>
+        <x:v>Whitley H55为细胞与组织培养提供低氧工作空间，可控制氧气、二氧化碳和湿度。研究人员可在腔体内的受控环境中操作培养物。
+可选隔板与滑门形成两个温区；三气版本使用氮气、氢气和二氧化碳。</x:v>
       </x:c>
       <x:c r="H10" s="8" t="str"/>
       <x:c r="I10" s="8" t="str"/>
@@ -626,16 +638,16 @@
         <x:v>待填写</x:v>
       </x:c>
       <x:c r="L10" s="3" t="str">
-        <x:v>操作、观察与培养任务</x:v>
+        <x:v>微生物操作与细胞或组织培养任务</x:v>
       </x:c>
       <x:c r="M10" s="3" t="str">
-        <x:v>温区与供气选项对应不同实验安排。PUN说明各区域承担什么任务，以及配置如何选择。</x:v>
+        <x:v>H55的任务、配置和选项分散在不同栏目。PUN用版本选择表将任务、使用条件、标准配置、选配和对应资料放在一起。</x:v>
       </x:c>
       <x:c r="N10" s="3" t="str">
-        <x:v>pun-IPAN已确认的任务、工作环境及观察操作说明。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="74" customHeight="1">
+        <x:v>两类低氧任务的产品资料、输入材料、实际操作、使用条件和验证记录；厌氧任务另列对应版本资料。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="164" customHeight="1">
       <x:c r="A11" s="3" t="str">
         <x:v>U04-004</x:v>
       </x:c>
@@ -649,15 +661,17 @@
         <x:v>工作空间、装载与人员布局</x:v>
       </x:c>
       <x:c r="E11" s="3" t="str">
-        <x:v>给真实尺寸图、板架/附件占用、工作区与培养区条件及人员任务。
-容量与具体板型、装载方式、工作区布局一起说明，并配真实装载图。</x:v>
+        <x:v>按版本和实际配置提供尺寸、板架与附件占用及装载图，注明可用操作区和人员安排。</x:v>
       </x:c>
       <x:c r="F11" s="3" t="str">
         <x:v>The A55 has two airlocks and two sets of ports for two operators. Access can use instant-access ports or a mixed port arrangement.
-https://www.dwscientific.com/whitley-anaerobic-workstations/whitley-a55-workstation</x:v>
+https://www.dwscientific.com/whitley-anaerobic-workstations/whitley-a55-workstation
+The H55 has four sleeved access ports and an airlock at each end. Two operators can work side by side, while the two airlocks provide routes for moving materials into and out of the workspace.
+https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
       </x:c>
       <x:c r="G11" s="3" t="str">
-        <x:v>A55设有两个气闸和两组操作口，可供两人使用；可选快速进入操作口或混合操作口配置。</x:v>
+        <x:v>A55设有两个气闸和两组操作口，可供两人使用；可选快速进入操作口或混合操作口配置。
+H55配有四个带袖套的操作口，两端各有一个气闸。两名操作人员可以并排工作，物料可通过两端气闸进出工作空间。</x:v>
       </x:c>
       <x:c r="H11" s="8" t="str"/>
       <x:c r="I11" s="8" t="str"/>
@@ -672,10 +686,10 @@
         <x:v>气闸和操作口数量说明了双人使用方式。PUN配人员位置、物料路径及装载示意图。</x:v>
       </x:c>
       <x:c r="N11" s="3" t="str">
-        <x:v>PUN布局—板架—载荷—操作人员数量的配置对照表。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="74" customHeight="1">
+        <x:v>分版本尺寸、装载图、板架或附件占用、可用操作区域与人员布局。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="164" customHeight="1">
       <x:c r="A12" s="11" t="str">
         <x:v>U04-005</x:v>
       </x:c>
@@ -689,14 +703,17 @@
         <x:v>转移、进出与暴露控制要求</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str">
-        <x:v>先说明需要解决的转移和操作问题；结构及环境控制能力均由PUN资料确认。</x:v>
+        <x:v>分别解释两版物料转移、进出与目标环境维持的需求，配自有操作示意和对应资料。</x:v>
       </x:c>
       <x:c r="F12" s="11" t="str">
         <x:v>A 36-litre airlock and automatic inner door support material transfer; the stated cycle is five minutes.
-https://www.dwscientific.com/whitley-anaerobic-workstations/whitley-a95-workstation</x:v>
+https://www.dwscientific.com/whitley-anaerobic-workstations/whitley-a95-workstation
+The H55 has four sleeved access ports and an airlock at each end. Two operators can work side by side, while the two airlocks provide routes for moving materials into and out of the workspace.
+https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
       </x:c>
       <x:c r="G12" s="11" t="str">
-        <x:v>36升气闸与自动内门用于物料转移，页面标示气闸循环为五分钟。</x:v>
+        <x:v>36升气闸与自动内门用于物料转移，页面标示气闸循环为五分钟。
+H55配有四个带袖套的操作口，两端各有一个气闸。两名操作人员可以并排工作，物料可通过两端气闸进出工作空间。</x:v>
       </x:c>
       <x:c r="H12" s="13" t="str"/>
       <x:c r="I12" s="13" t="str"/>
@@ -711,10 +728,10 @@
         <x:v>气闸容积和循环时间支持转移评估。PUN同时交代物料、装载方式、测试条件和操作限制。</x:v>
       </x:c>
       <x:c r="N12" s="3" t="str">
-        <x:v>PUN布局—板架—载荷—操作人员数量的配置对照表。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="74" customHeight="1">
+        <x:v>分版本物料转移、进出及环境维持的真实流程和测试条件。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="164" customHeight="1">
       <x:c r="A13" s="3" t="str">
         <x:v>U04-006</x:v>
       </x:c>
@@ -728,14 +745,17 @@
         <x:v>气闸容量与物料转移</x:v>
       </x:c>
       <x:c r="E13" s="3" t="str">
-        <x:v>补材料尺寸/载荷、气锁或转移结构及核实后的步骤图；不借用竞品周期或联锁参数。</x:v>
+        <x:v>按版本列转移结构、物料规格和载荷；周期与容量写清条件，并引用对应PUN资料。</x:v>
       </x:c>
       <x:c r="F13" s="3" t="str">
         <x:v>The airlock holds twenty 90 mm plates or three 500 mL bottles. The stated transfer cycle is twenty seconds.
-https://www.dwscientific.com/whitley-anaerobic-workstations/whitley-a25-workstation</x:v>
+https://www.dwscientific.com/whitley-anaerobic-workstations/whitley-a25-workstation
+The H55 has four sleeved access ports and an airlock at each end. Two operators can work side by side, while the two airlocks provide routes for moving materials into and out of the workspace.
+https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
       </x:c>
       <x:c r="G13" s="3" t="str">
-        <x:v>气闸可放二十块90毫米平板或三个500毫升瓶，页面标示转移循环为二十秒。</x:v>
+        <x:v>气闸可放二十块90毫米平板或三个500毫升瓶，页面标示转移循环为二十秒。
+H55配有四个带袖套的操作口，两端各有一个气闸。两名操作人员可以并排工作，物料可通过两端气闸进出工作空间。</x:v>
       </x:c>
       <x:c r="H13" s="8" t="str"/>
       <x:c r="I13" s="8" t="str"/>
@@ -750,10 +770,10 @@
         <x:v>平板与培养瓶的装载示例容易理解。PUN给出自己常用物料的装载照片及转移条件。</x:v>
       </x:c>
       <x:c r="N13" s="3" t="str">
-        <x:v>PUN布局—板架—载荷—操作人员数量的配置对照表。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="74" customHeight="1">
+        <x:v>实际转移结构、气闸可用尺寸、载荷与板型；如写周期，提供对应条件与测试资料。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="164" customHeight="1">
       <x:c r="A14" s="3" t="str">
         <x:v>U04-007</x:v>
       </x:c>
@@ -767,14 +787,17 @@
         <x:v>操作口与人员操作</x:v>
       </x:c>
       <x:c r="E14" s="3" t="str">
-        <x:v>以操作可达性、人员布局、端口及选配差异提出核对项；未确认项留给工程审阅。</x:v>
+        <x:v>配实际操作口和人员布局图，说明操作可达区域、进出方式及对应版本或选配。</x:v>
       </x:c>
       <x:c r="F14" s="3" t="str">
         <x:v>The compact A25 offers instant-access or sleeved ports and an interlocked airlock for material transfer.
-https://www.dwscientific.com/whitley-anaerobic-workstations/whitley-a25-workstation</x:v>
+https://www.dwscientific.com/whitley-anaerobic-workstations/whitley-a25-workstation
+The H55 has four sleeved access ports and an airlock at each end. Two operators can work side by side, while the two airlocks provide routes for moving materials into and out of the workspace.
+https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
       </x:c>
       <x:c r="G14" s="3" t="str">
-        <x:v>紧凑型A25可选快速进入或袖套式操作口，并通过互锁气闸转移物料。</x:v>
+        <x:v>紧凑型A25可选快速进入或袖套式操作口，并通过互锁气闸转移物料。
+H55配有四个带袖套的操作口，两端各有一个气闸。两名操作人员可以并排工作，物料可通过两端气闸进出工作空间。</x:v>
       </x:c>
       <x:c r="H14" s="8" t="str"/>
       <x:c r="I14" s="8" t="str"/>
@@ -789,7 +812,7 @@
         <x:v>不同操作口对应不同进入方式。PUN解释何时选择哪种配置，以及操作人员需要怎样准备。</x:v>
       </x:c>
       <x:c r="N14" s="3" t="str">
-        <x:v>pun-IPAN实际气闸、端口、载荷和操作边界。</x:v>
+        <x:v>各版本操作口、人员布局及进出方式的照片、示意图和配置资料。</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="74" customHeight="1">
@@ -806,7 +829,7 @@
         <x:v>气体、公用设施与场地准备</x:v>
       </x:c>
       <x:c r="E15" s="11" t="str">
-        <x:v>列应核实的供气、电源、空间、环境与安装条件；数值必须来自PUN批准文档。</x:v>
+        <x:v>按版本与配置分别列气源、电源、场地和环境准备事项，关联对应安装文件。</x:v>
       </x:c>
       <x:c r="F15" s="11" t="str">
         <x:v>Separate installation documents are linked for A95 and A95TG, so installation requirements must be matched to the actual variant.
@@ -828,10 +851,10 @@
         <x:v>安装文件按变型区分。PUN让供气、电源、环境和尺寸资料与具体型号对应。</x:v>
       </x:c>
       <x:c r="N15" s="3" t="str">
-        <x:v>PUN气体/电源/环境/安装图和工程责任清单。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="74" customHeight="1">
+        <x:v>各版本气源、电源、场地和环境准备文件及适用型号。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="179" customHeight="1">
       <x:c r="A16" s="3" t="str">
         <x:v>U04-009</x:v>
       </x:c>
@@ -839,21 +862,23 @@
         <x:v>H3</x:v>
       </x:c>
       <x:c r="C16" s="3" t="str">
-        <x:v>Gas Supply, Environment and Installation Data</x:v>
+        <x:v>Version-Specific Gas, Environment and Installation Data</x:v>
       </x:c>
       <x:c r="D16" s="3" t="str">
-        <x:v>供气、环境与安装资料</x:v>
+        <x:v>分版本的供气、环境与安装资料</x:v>
       </x:c>
       <x:c r="E16" s="3" t="str">
-        <x:v>作者补气体规格、用量条件、空间与环境要求及文档版本，禁止使用竞品值。
-安装资料按实际型号和配置分别列出文件名称、版本、气源、电源与现场净空。</x:v>
+        <x:v>按版本列气源、电源、空间和实际控制或监测项目，配安装文件；氧浓度、温控及CO2等数据引用对应型号资料。</x:v>
       </x:c>
       <x:c r="F16" s="3" t="str">
         <x:v>An optional divider and sliding door create two temperature zones; a three-gas variant uses nitrogen, hydrogen and carbon dioxide.
-https://www.dwscientific.com/whitley-anaerobic-workstations/whitley-a55-workstation</x:v>
+https://www.dwscientific.com/whitley-anaerobic-workstations/whitley-a55-workstation
+A touchscreen displays oxygen, carbon dioxide, temperature, humidity and airlock status. Data logging and oxygen profiling are available as options, so these recording functions can be specified alongside the workstation configuration.
+https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
       </x:c>
       <x:c r="G16" s="3" t="str">
-        <x:v>可选隔板与滑门形成两个温区；三气版本使用氮气、氢气和二氧化碳。</x:v>
+        <x:v>可选隔板与滑门形成两个温区；三气版本使用氮气、氢气和二氧化碳。
+触摸屏显示氧气、二氧化碳、温度、湿度和气闸状态。数据记录与氧浓度曲线属于可选功能，客户可在确定工作站配置时一并选择。</x:v>
       </x:c>
       <x:c r="H16" s="8" t="str"/>
       <x:c r="I16" s="8" t="str"/>
@@ -862,13 +887,13 @@
         <x:v>待填写</x:v>
       </x:c>
       <x:c r="L16" s="3" t="str">
-        <x:v>供气、环境与安装资料</x:v>
+        <x:v>分版本的供气、环境与安装资料</x:v>
       </x:c>
       <x:c r="M16" s="3" t="str">
         <x:v>三气版本把气体要求单独写出。PUN列出气源、连接方式和现场需要准备的设施。</x:v>
       </x:c>
       <x:c r="N16" s="3" t="str">
-        <x:v>PUN气体/电源/环境/安装图和工程责任清单。</x:v>
+        <x:v>对应版本安装文件及实际控制或监测项目清单；氧浓度、温控、CO2等功能与数值引用对应型号资料。</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="74" customHeight="1">
@@ -885,7 +910,7 @@
         <x:v>工程接口与责任审阅</x:v>
       </x:c>
       <x:c r="E17" s="3" t="str">
-        <x:v>列场地交接、安装责任、未决接口及审核人；不承诺未确认的交付范围。</x:v>
+        <x:v>列客户与供应商负责事项、场地接口和审核联系人，明确版本及适用文件。</x:v>
       </x:c>
       <x:c r="F17" s="3" t="str">
         <x:v>Options include internal electrical sockets, microscope accommodation and a single-plate entry system.
@@ -907,10 +932,10 @@
         <x:v>内部电源、显微镜和进入系统与具体任务相连。PUN说明选配接口、适用条件和双方责任。</x:v>
       </x:c>
       <x:c r="N17" s="3" t="str">
-        <x:v>PUN气体/电源/环境/安装图和工程责任清单。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="74" customHeight="1">
+        <x:v>场地与设备接口、客户和供应商职责、工程审核联系人及适用文件。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="179" customHeight="1">
       <x:c r="A18" s="11" t="str">
         <x:v>U04-011</x:v>
       </x:c>
@@ -918,20 +943,23 @@
         <x:v>H2</x:v>
       </x:c>
       <x:c r="C18" s="12" t="str">
-        <x:v>Configuration Evidence and Acceptance Planning</x:v>
+        <x:v>Version Selection, Configuration and Acceptance Planning</x:v>
       </x:c>
       <x:c r="D18" s="12" t="str">
-        <x:v>配置证据与验收规划</x:v>
+        <x:v>版本选择、配置与验收规划</x:v>
       </x:c>
       <x:c r="E18" s="11" t="str">
-        <x:v>把标准/选配、受控规格、性能证据及验收判据一起呈现。</x:v>
+        <x:v>把任务、版本、标准配置与选配、验收资料放在同一张对照表，便于技术与采购共同核对。</x:v>
       </x:c>
       <x:c r="F18" s="11" t="str">
         <x:v>A55 plate capacity varies with carriers, accessories and options; the page lists 1,080–1,200 plates rather than one unconditional figure.
-https://www.dwscientific.com/whitley-anaerobic-workstations/whitley-a55-workstation</x:v>
+https://www.dwscientific.com/whitley-anaerobic-workstations/whitley-a55-workstation
+A touchscreen displays oxygen, carbon dioxide, temperature, humidity and airlock status. Data logging and oxygen profiling are available as options, so these recording functions can be specified alongside the workstation configuration.
+https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
       </x:c>
       <x:c r="G18" s="11" t="str">
-        <x:v>A55容量随载架、附件和选项变化；页面列示1,080–1,200块平板，而非无条件的单一容量。</x:v>
+        <x:v>A55容量随载架、附件和选项变化；页面列示1,080–1,200块平板，而非无条件的单一容量。
+触摸屏显示氧气、二氧化碳、温度、湿度和气闸状态。数据记录与氧浓度曲线属于可选功能，客户可在确定工作站配置时一并选择。</x:v>
       </x:c>
       <x:c r="H18" s="13" t="str"/>
       <x:c r="I18" s="13" t="str"/>
@@ -940,17 +968,16 @@
         <x:v>待填写</x:v>
       </x:c>
       <x:c r="L18" s="3" t="str">
-        <x:v>配置证据与验收规划</x:v>
+        <x:v>版本选择、配置与验收规划</x:v>
       </x:c>
       <x:c r="M18" s="3" t="str">
         <x:v>容量随载架和附件变化。PUN提供按布局列出的容量、可用空间和验收条件。</x:v>
       </x:c>
       <x:c r="N18" s="3" t="str">
-        <x:v>PUN气闸/环境性能主张的测试条件、基线、样本和复核。
-PUN下载链接、版本、权限与可用性检查。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="74" customHeight="1">
+        <x:v>任务、版本、标准配置、选配及验收资料的完整对照表。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="269" customHeight="1">
       <x:c r="A19" s="3" t="str">
         <x:v>U04-012</x:v>
       </x:c>
@@ -958,20 +985,26 @@
         <x:v>H3</x:v>
       </x:c>
       <x:c r="C19" s="3" t="str">
-        <x:v>Standard Configuration and Options</x:v>
+        <x:v>Anaerobic and Hypoxic Version Configurations</x:v>
       </x:c>
       <x:c r="D19" s="3" t="str">
-        <x:v>标准配置与可选项</x:v>
+        <x:v>厌氧与低氧版本配置</x:v>
       </x:c>
       <x:c r="E19" s="3" t="str">
-        <x:v>逐项说明标配/选配、适用版本和文件；每条给PUN证据或待确认状态。</x:v>
+        <x:v>按版本列标准配置、可选模块和适用任务；低氧版分别标注微需氧微生物、细胞或组织培养的资料适用范围。</x:v>
       </x:c>
       <x:c r="F19" s="3" t="str">
         <x:v>Touchscreen controls display temperature and humidity; monitoring, data logging and internal power are configuration-dependent options.
-https://www.dwscientific.com/whitley-anaerobic-workstations/whitley-a25-workstation</x:v>
+https://www.dwscientific.com/whitley-anaerobic-workstations/whitley-a25-workstation
+The Whitley H55 provides a low-oxygen workspace for cell and tissue culture, with controls for oxygen, carbon dioxide and humidity. Researchers can work with cultures inside the controlled chamber environment.
+https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation
+A touchscreen displays oxygen, carbon dioxide, temperature, humidity and airlock status. Data logging and oxygen profiling are available as options, so these recording functions can be specified alongside the workstation configuration.
+https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
       </x:c>
       <x:c r="G19" s="3" t="str">
-        <x:v>触屏控制显示温度和湿度；监测、数据记录和内部供电属于按配置提供的选项。</x:v>
+        <x:v>触屏控制显示温度和湿度；监测、数据记录和内部供电属于按配置提供的选项。
+Whitley H55为细胞与组织培养提供低氧工作空间，可控制氧气、二氧化碳和湿度。研究人员可在腔体内的受控环境中操作培养物。
+触摸屏显示氧气、二氧化碳、温度、湿度和气闸状态。数据记录与氧浓度曲线属于可选功能，客户可在确定工作站配置时一并选择。</x:v>
       </x:c>
       <x:c r="H19" s="8" t="str"/>
       <x:c r="I19" s="8" t="str"/>
@@ -980,17 +1013,16 @@
         <x:v>待填写</x:v>
       </x:c>
       <x:c r="L19" s="3" t="str">
-        <x:v>标准配置与可选项</x:v>
+        <x:v>厌氧与低氧版本配置</x:v>
       </x:c>
       <x:c r="M19" s="3" t="str">
-        <x:v>监测、记录和内部供电作为配置项说明。PUN用对照表区分标准功能与可选功能。</x:v>
+        <x:v>H55的任务、配置和选项分散在不同栏目。PUN用版本选择表将任务、使用条件、标准配置、选配和对应资料放在一起。</x:v>
       </x:c>
       <x:c r="N19" s="3" t="str">
-        <x:v>PUN布局—板架—载荷—操作人员数量的配置对照表。
-PUN下载链接、版本、权限与可用性检查。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="89" customHeight="1">
+        <x:v>各版本配置清单；低氧版两类任务的资料适用范围；模块与型号对应关系。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="179" customHeight="1">
       <x:c r="A20" s="3" t="str">
         <x:v>U04-013</x:v>
       </x:c>
@@ -998,21 +1030,23 @@
         <x:v>H3</x:v>
       </x:c>
       <x:c r="C20" s="3" t="str">
-        <x:v>Anaerobic Performance Evidence and Enquiries</x:v>
+        <x:v>Oxygen-Control Performance Evidence and Enquiries</x:v>
       </x:c>
       <x:c r="D20" s="3" t="str">
-        <x:v>厌氧性能证据与咨询</x:v>
+        <x:v>氧环境控制性能证据与咨询</x:v>
       </x:c>
       <x:c r="E20" s="3" t="str">
-        <x:v>说明实际监测项目、记录频率、下载格式和异常处理；为环境或转移性能提供测试条件、数据及经过审核的资料。
-性能数字旁列测试配置、载荷、供气、环境、计时判据、重复次数及报告版本。</x:v>
+        <x:v>展示各版本实际测试条件、结果和记录样张，说明环境控制与转移的验收依据，并列客户需提供的样本背景和配置需求。</x:v>
       </x:c>
       <x:c r="F20" s="3" t="str">
         <x:v>An optional integrated monitor records anaerobic conditions and supports data download.
-https://www.dwscientific.com/whitley-anaerobic-workstations/whitley-a95-workstation</x:v>
+https://www.dwscientific.com/whitley-anaerobic-workstations/whitley-a95-workstation
+A touchscreen displays oxygen, carbon dioxide, temperature, humidity and airlock status. Data logging and oxygen profiling are available as options, so these recording functions can be specified alongside the workstation configuration.
+https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
       </x:c>
       <x:c r="G20" s="3" t="str">
-        <x:v>可选的集成监测器记录厌氧条件，并支持数据下载。</x:v>
+        <x:v>可选的集成监测器记录厌氧条件，并支持数据下载。
+触摸屏显示氧气、二氧化碳、温度、湿度和气闸状态。数据记录与氧浓度曲线属于可选功能，客户可在确定工作站配置时一并选择。</x:v>
       </x:c>
       <x:c r="H20" s="8" t="str"/>
       <x:c r="I20" s="8" t="str"/>
@@ -1021,13 +1055,13 @@
         <x:v>待填写</x:v>
       </x:c>
       <x:c r="L20" s="3" t="str">
-        <x:v>厌氧性能证据与咨询</x:v>
+        <x:v>氧环境控制性能证据与咨询</x:v>
       </x:c>
       <x:c r="M20" s="3" t="str">
-        <x:v>监测记录和数据下载提供了结果依据。PUN展示监测项目、记录样张、测试条件及咨询所需信息。</x:v>
+        <x:v>竞争页说明了监测或记录功能，但客户仍需核对哪些是标准配置、哪些是选配。PUN可配真实记录样张，并写清测试条件及功能适用版本。</x:v>
       </x:c>
       <x:c r="N20" s="3" t="str">
-        <x:v>环境与转移测试条件、样本和结果；监测或导出样张；适用型号及文件版本。</x:v>
+        <x:v>实际环境控制与转移测试条件、结果和记录样张，注明型号、软件及文件版本；只展示已确认功能。</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -4619,7 +4653,7 @@
       </x:c>
       <x:c r="B3" s="3"/>
       <x:c r="C3" s="3" t="str">
-        <x:v>pun-IPAN Anaerobic Workstations</x:v>
+        <x:v>pun-IPAN Anaerobic and Hypoxic Workstations</x:v>
       </x:c>
       <x:c r="D3" s="3" t="str">
         <x:v>有效规划模板，资料齐备后进入开发</x:v>
@@ -4733,10 +4767,10 @@
         <x:v>U04-001</x:v>
       </x:c>
       <x:c r="B8" s="3" t="str">
-        <x:v>pun-IPAN Anaerobic Workstations</x:v>
+        <x:v>pun-IPAN Anaerobic and Hypoxic Workstations</x:v>
       </x:c>
       <x:c r="C8" s="3" t="str">
-        <x:v>pun-IPAN 厌氧工作站</x:v>
+        <x:v>pun-IPAN 厌氧与低氧工作站</x:v>
       </x:c>
       <x:c r="D8" s="8" t="str"/>
       <x:c r="E8" s="8" t="str"/>
@@ -4756,10 +4790,10 @@
         <x:v>U04-002</x:v>
       </x:c>
       <x:c r="B9" s="3" t="str">
-        <x:v>Anaerobic Handling Tasks and Workspace Planning</x:v>
+        <x:v>Choose the Anaerobic or Hypoxic Version</x:v>
       </x:c>
       <x:c r="C9" s="3" t="str">
-        <x:v>厌氧操作任务与工作空间规划</x:v>
+        <x:v>选择厌氧或低氧版本</x:v>
       </x:c>
       <x:c r="D9" s="8" t="str"/>
       <x:c r="E9" s="8" t="str"/>
@@ -4779,10 +4813,10 @@
         <x:v>U04-003</x:v>
       </x:c>
       <x:c r="B10" s="3" t="str">
-        <x:v>Manipulation, Observation and Culture Tasks</x:v>
+        <x:v>Microbial Handling and Cell or Tissue Culture Tasks</x:v>
       </x:c>
       <x:c r="C10" s="3" t="str">
-        <x:v>操作、观察与培养任务</x:v>
+        <x:v>微生物操作与细胞或组织培养任务</x:v>
       </x:c>
       <x:c r="D10" s="8" t="str"/>
       <x:c r="E10" s="8" t="str"/>
@@ -4828,7 +4862,7 @@
         <x:v>Transfer, Access and Exposure-Control Requirements</x:v>
       </x:c>
       <x:c r="C12" s="3" t="str">
-        <x:v>转移、访问及暴露控制要求</x:v>
+        <x:v>转移、进出与暴露控制要求</x:v>
       </x:c>
       <x:c r="D12" s="8" t="str"/>
       <x:c r="E12" s="8" t="str"/>
@@ -4917,10 +4951,10 @@
         <x:v>U04-009</x:v>
       </x:c>
       <x:c r="B16" s="3" t="str">
-        <x:v>Gas Supply, Environment and Installation Data</x:v>
+        <x:v>Version-Specific Gas, Environment and Installation Data</x:v>
       </x:c>
       <x:c r="C16" s="3" t="str">
-        <x:v>供气、环境与安装资料</x:v>
+        <x:v>分版本的供气、环境与安装资料</x:v>
       </x:c>
       <x:c r="D16" s="8" t="str"/>
       <x:c r="E16" s="8" t="str"/>
@@ -4963,10 +4997,10 @@
         <x:v>U04-011</x:v>
       </x:c>
       <x:c r="B18" s="3" t="str">
-        <x:v>Configuration Evidence and Acceptance Planning</x:v>
+        <x:v>Version Selection, Configuration and Acceptance Planning</x:v>
       </x:c>
       <x:c r="C18" s="3" t="str">
-        <x:v>配置证据与验收规划</x:v>
+        <x:v>版本选择、配置与验收规划</x:v>
       </x:c>
       <x:c r="D18" s="8" t="str"/>
       <x:c r="E18" s="8" t="str"/>
@@ -4986,10 +5020,10 @@
         <x:v>U04-012</x:v>
       </x:c>
       <x:c r="B19" s="3" t="str">
-        <x:v>Standard Configuration and Options</x:v>
+        <x:v>Anaerobic and Hypoxic Version Configurations</x:v>
       </x:c>
       <x:c r="C19" s="3" t="str">
-        <x:v>标准配置与可选项</x:v>
+        <x:v>厌氧与低氧版本配置</x:v>
       </x:c>
       <x:c r="D19" s="8" t="str"/>
       <x:c r="E19" s="8" t="str"/>
@@ -5009,10 +5043,10 @@
         <x:v>U04-013</x:v>
       </x:c>
       <x:c r="B20" s="3" t="str">
-        <x:v>Anaerobic Performance Evidence and Enquiries</x:v>
+        <x:v>Oxygen-Control Performance Evidence and Enquiries</x:v>
       </x:c>
       <x:c r="C20" s="3" t="str">
-        <x:v>厌氧性能证据与咨询</x:v>
+        <x:v>氧环境控制性能证据与咨询</x:v>
       </x:c>
       <x:c r="D20" s="8" t="str"/>
       <x:c r="E20" s="8" t="str"/>
@@ -8384,7 +8418,7 @@
       </x:c>
       <x:c r="B3" s="3"/>
       <x:c r="C3" s="3" t="str">
-        <x:v>pun-IPAN Anaerobic Workstations</x:v>
+        <x:v>pun-IPAN Anaerobic and Hypoxic Workstations</x:v>
       </x:c>
       <x:c r="D3" s="3" t="str">
         <x:v>有效规划模板，资料齐备后进入开发</x:v>
@@ -8484,10 +8518,10 @@
         <x:v>h1</x:v>
       </x:c>
       <x:c r="C9" s="3" t="str">
-        <x:v>pun-IPAN Anaerobic Workstations</x:v>
+        <x:v>pun-IPAN Anaerobic and Hypoxic Workstations</x:v>
       </x:c>
       <x:c r="D9" s="3" t="str">
-        <x:v>pun-IPAN 厌氧工作站</x:v>
+        <x:v>pun-IPAN 厌氧与低氧工作站</x:v>
       </x:c>
       <x:c r="E9" s="8" t="str"/>
       <x:c r="F9" s="3" t="str">
@@ -8620,7 +8654,7 @@
         <x:v>primary_keyword</x:v>
       </x:c>
       <x:c r="C16" s="3" t="str">
-        <x:v>anaerobic chamber; anaerobic workstation</x:v>
+        <x:v>anaerobic workstation; hypoxia workstation; hypoxic workstation</x:v>
       </x:c>
       <x:c r="D16" s="3" t="str"/>
       <x:c r="E16" s="8" t="str"/>
@@ -8654,7 +8688,7 @@
         <x:v>intent</x:v>
       </x:c>
       <x:c r="C18" s="3" t="str">
-        <x:v>评估厌氧工作环境与安装需求</x:v>
+        <x:v>选择pun-IPAN厌氧或低氧版本，核对实际任务、工作空间、转移、配置和安装需求；低氧版分别回应微需氧微生物、细胞与组织培养。</x:v>
       </x:c>
       <x:c r="D18" s="3" t="str"/>
       <x:c r="E18" s="8" t="str"/>
@@ -8672,10 +8706,10 @@
         <x:v>title_tag</x:v>
       </x:c>
       <x:c r="C19" s="3" t="str">
-        <x:v>pun-IPAN Anaerobic Workstations | Punmicro</x:v>
+        <x:v>pun-IPAN Anaerobic and Hypoxic Workstations | Punmicro</x:v>
       </x:c>
       <x:c r="D19" s="3" t="str">
-        <x:v>pun-IPAN 厌氧工作站 | Punmicro</x:v>
+        <x:v>pun-IPAN 厌氧与低氧工作站 | Punmicro</x:v>
       </x:c>
       <x:c r="E19" s="8" t="str"/>
       <x:c r="F19" s="3" t="str">
@@ -8696,11 +8730,9 @@
         <x:v>meta_description</x:v>
       </x:c>
       <x:c r="C20" s="3" t="str">
-        <x:v>Explore pun-IPAN anaerobic workstation requirements for laboratory handling. Discuss workspace, transfer routines and model-specific installation needs.</x:v>
-      </x:c>
-      <x:c r="D20" s="3" t="str">
-        <x:v>了解实验室操作对 pun-IPAN 厌氧工作站的需求，沟通工作空间、物品转移流程及具体型号的安装条件。</x:v>
-      </x:c>
+        <x:v>Explore pun-IPAN anaerobic and hypoxic workstation options for microbial handling and cell or tissue culture. Compare tasks, configurations and installation needs.</x:v>
+      </x:c>
+      <x:c r="D20" s="3" t="str"/>
       <x:c r="E20" s="8" t="str"/>
       <x:c r="F20" s="3" t="str">
         <x:v>准确摘要，不固定字符数；搜索引擎可能重新生成片段。</x:v>
@@ -8794,10 +8826,10 @@
         <x:v>og:title</x:v>
       </x:c>
       <x:c r="C25" s="3" t="str">
-        <x:v>pun-IPAN Anaerobic Workstations | Punmicro</x:v>
+        <x:v>pun-IPAN Anaerobic and Hypoxic Workstations | Punmicro</x:v>
       </x:c>
       <x:c r="D25" s="3" t="str">
-        <x:v>pun-IPAN 厌氧工作站 | Punmicro</x:v>
+        <x:v>pun-IPAN 厌氧与低氧工作站 | Punmicro</x:v>
       </x:c>
       <x:c r="E25" s="8" t="str"/>
       <x:c r="F25" s="3" t="str">
@@ -8818,11 +8850,9 @@
         <x:v>og:description</x:v>
       </x:c>
       <x:c r="C26" s="3" t="str">
-        <x:v>Explore pun-IPAN anaerobic workstation requirements for laboratory handling. Discuss workspace, transfer routines and model-specific installation needs.</x:v>
-      </x:c>
-      <x:c r="D26" s="3" t="str">
-        <x:v>了解实验室操作对 pun-IPAN 厌氧工作站的需求，沟通工作空间、物品转移流程及具体型号的安装条件。</x:v>
-      </x:c>
+        <x:v>Explore pun-IPAN anaerobic and hypoxic workstation options for microbial handling and cell or tissue culture. Compare tasks, configurations and installation needs.</x:v>
+      </x:c>
+      <x:c r="D26" s="3" t="str"/>
       <x:c r="E26" s="8" t="str"/>
       <x:c r="F26" s="3" t="str">
         <x:v>可编辑，需与内容相符。</x:v>
@@ -8930,10 +8960,10 @@
         <x:v>twitter:title</x:v>
       </x:c>
       <x:c r="C32" s="3" t="str">
-        <x:v>pun-IPAN Anaerobic Workstations | Punmicro</x:v>
+        <x:v>pun-IPAN Anaerobic and Hypoxic Workstations | Punmicro</x:v>
       </x:c>
       <x:c r="D32" s="3" t="str">
-        <x:v>pun-IPAN 厌氧工作站 | Punmicro</x:v>
+        <x:v>pun-IPAN 厌氧与低氧工作站 | Punmicro</x:v>
       </x:c>
       <x:c r="E32" s="8" t="str"/>
       <x:c r="F32" s="3" t="str">
@@ -8954,11 +8984,9 @@
         <x:v>twitter:description</x:v>
       </x:c>
       <x:c r="C33" s="3" t="str">
-        <x:v>Explore pun-IPAN anaerobic workstation requirements for laboratory handling. Discuss workspace, transfer routines and model-specific installation needs.</x:v>
-      </x:c>
-      <x:c r="D33" s="3" t="str">
-        <x:v>了解实验室操作对 pun-IPAN 厌氧工作站的需求，沟通工作空间、物品转移流程及具体型号的安装条件。</x:v>
-      </x:c>
+        <x:v>Explore pun-IPAN anaerobic and hypoxic workstation options for microbial handling and cell or tissue culture. Compare tasks, configurations and installation needs.</x:v>
+      </x:c>
+      <x:c r="D33" s="3" t="str"/>
       <x:c r="E33" s="8" t="str"/>
       <x:c r="F33" s="3" t="str">
         <x:v>可沿用已审核摘要。</x:v>
@@ -9320,7 +9348,7 @@
         <x:v>required_evidence</x:v>
       </x:c>
       <x:c r="C55" s="3" t="str">
-        <x:v>适用条件、容量、气体/环境参数与维护资料由工程确认；地区支持不默认全球</x:v>
+        <x:v>厌氧与低氧版本及低氧版两类任务已有用户业务确认；发布时由研发提供对应型号的适用条件、配置、容量、气体与环境参数、测试和维护资料。氧浓度、温控、CO2等功能与数值按实际资料填写；地区支持另行确认。</x:v>
       </x:c>
       <x:c r="D55" s="3" t="str"/>
       <x:c r="E55" s="8" t="str"/>
@@ -12911,135 +12939,906 @@
         <x:v>https://www.dwscientific.com/whitley-anaerobic-workstations/whitley-a25-workstation</x:v>
       </x:c>
     </x:row>
-    <x:row r="228">
-      <x:c r="A228" s="3"/>
-      <x:c r="B228" s="3"/>
-      <x:c r="C228" s="3"/>
-      <x:c r="D228" s="3"/>
-      <x:c r="E228" s="3"/>
-      <x:c r="F228" s="3"/>
-      <x:c r="G228" s="3"/>
-      <x:c r="H228" s="3"/>
-    </x:row>
-    <x:row r="229">
-      <x:c r="A229" s="3"/>
-      <x:c r="B229" s="3"/>
-      <x:c r="C229" s="3"/>
-      <x:c r="D229" s="3"/>
-      <x:c r="E229" s="3"/>
-      <x:c r="F229" s="3"/>
-      <x:c r="G229" s="3"/>
-      <x:c r="H229" s="3"/>
-    </x:row>
-    <x:row r="230">
-      <x:c r="A230" s="3"/>
-      <x:c r="B230" s="3"/>
-      <x:c r="C230" s="3"/>
-      <x:c r="D230" s="3"/>
-      <x:c r="E230" s="3"/>
-      <x:c r="F230" s="3"/>
-      <x:c r="G230" s="3"/>
-      <x:c r="H230" s="3"/>
-    </x:row>
-    <x:row r="231">
-      <x:c r="A231" s="3"/>
-      <x:c r="B231" s="3"/>
-      <x:c r="C231" s="3"/>
-      <x:c r="D231" s="3"/>
-      <x:c r="E231" s="3"/>
-      <x:c r="F231" s="3"/>
-      <x:c r="G231" s="3"/>
-      <x:c r="H231" s="3"/>
-    </x:row>
-    <x:row r="232">
-      <x:c r="A232" s="3"/>
-      <x:c r="B232" s="3"/>
-      <x:c r="C232" s="3"/>
-      <x:c r="D232" s="3"/>
-      <x:c r="E232" s="3"/>
-      <x:c r="F232" s="3"/>
-      <x:c r="G232" s="3"/>
-      <x:c r="H232" s="3"/>
-    </x:row>
-    <x:row r="233">
-      <x:c r="A233" s="3"/>
-      <x:c r="B233" s="3"/>
-      <x:c r="C233" s="3"/>
-      <x:c r="D233" s="3"/>
-      <x:c r="E233" s="3"/>
-      <x:c r="F233" s="3"/>
-      <x:c r="G233" s="3"/>
-      <x:c r="H233" s="3"/>
-    </x:row>
-    <x:row r="234">
-      <x:c r="A234" s="3"/>
-      <x:c r="B234" s="3"/>
-      <x:c r="C234" s="3"/>
-      <x:c r="D234" s="3"/>
-      <x:c r="E234" s="3"/>
-      <x:c r="F234" s="3"/>
-      <x:c r="G234" s="3"/>
-      <x:c r="H234" s="3"/>
-    </x:row>
-    <x:row r="235">
-      <x:c r="A235" s="3"/>
-      <x:c r="B235" s="3"/>
-      <x:c r="C235" s="3"/>
-      <x:c r="D235" s="3"/>
-      <x:c r="E235" s="3"/>
-      <x:c r="F235" s="3"/>
-      <x:c r="G235" s="3"/>
-      <x:c r="H235" s="3"/>
-    </x:row>
-    <x:row r="236">
-      <x:c r="A236" s="3"/>
-      <x:c r="B236" s="3"/>
-      <x:c r="C236" s="3"/>
-      <x:c r="D236" s="3"/>
-      <x:c r="E236" s="3"/>
-      <x:c r="F236" s="3"/>
-      <x:c r="G236" s="3"/>
-      <x:c r="H236" s="3"/>
-    </x:row>
-    <x:row r="237">
-      <x:c r="A237" s="3"/>
-      <x:c r="B237" s="3"/>
-      <x:c r="C237" s="3"/>
-      <x:c r="D237" s="3"/>
-      <x:c r="E237" s="3"/>
-      <x:c r="F237" s="3"/>
-      <x:c r="G237" s="3"/>
-      <x:c r="H237" s="3"/>
-    </x:row>
-    <x:row r="238">
-      <x:c r="A238" s="3"/>
-      <x:c r="B238" s="3"/>
-      <x:c r="C238" s="3"/>
-      <x:c r="D238" s="3"/>
-      <x:c r="E238" s="3"/>
-      <x:c r="F238" s="3"/>
-      <x:c r="G238" s="3"/>
-      <x:c r="H238" s="3"/>
-    </x:row>
-    <x:row r="239">
-      <x:c r="A239" s="3"/>
-      <x:c r="B239" s="3"/>
-      <x:c r="C239" s="3"/>
-      <x:c r="D239" s="3"/>
-      <x:c r="E239" s="3"/>
-      <x:c r="F239" s="3"/>
-      <x:c r="G239" s="3"/>
-      <x:c r="H239" s="3"/>
-    </x:row>
-    <x:row r="240">
-      <x:c r="A240" s="3"/>
-      <x:c r="B240" s="3"/>
-      <x:c r="C240" s="3"/>
-      <x:c r="D240" s="3"/>
-      <x:c r="E240" s="3"/>
-      <x:c r="F240" s="3"/>
-      <x:c r="G240" s="3"/>
-      <x:c r="H240" s="3"/>
+    <x:row r="228" ht="48" customHeight="1">
+      <x:c r="A228" s="3" t="str">
+        <x:v>竞品分析</x:v>
+      </x:c>
+      <x:c r="B228" s="3" t="str">
+        <x:v>DWS-H55 · 页面类型</x:v>
+      </x:c>
+      <x:c r="C228" s="3" t="str"/>
+      <x:c r="D228" s="3" t="str"/>
+      <x:c r="E228" s="3" t="str"/>
+      <x:c r="F228" s="3" t="str"/>
+      <x:c r="G228" s="3" t="str">
+        <x:v>产品介绍页</x:v>
+      </x:c>
+      <x:c r="H228" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229" ht="48" customHeight="1">
+      <x:c r="A229" s="3" t="str">
+        <x:v>竞品分析</x:v>
+      </x:c>
+      <x:c r="B229" s="3" t="str">
+        <x:v>DWS-H55 · 页面解决的问题</x:v>
+      </x:c>
+      <x:c r="C229" s="3" t="str"/>
+      <x:c r="D229" s="3" t="str"/>
+      <x:c r="E229" s="3" t="str"/>
+      <x:c r="F229" s="3" t="str"/>
+      <x:c r="G229" s="3" t="str">
+        <x:v>H55先说明低氧细胞与组织培养任务，再用双人操作、两端气闸、环境参数显示、选配和安装资料帮助读者评估设备。</x:v>
+      </x:c>
+      <x:c r="H229" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230" ht="48" customHeight="1">
+      <x:c r="A230" s="3" t="str">
+        <x:v>竞品分析</x:v>
+      </x:c>
+      <x:c r="B230" s="3" t="str">
+        <x:v>DWS-H55 · 内容顺序</x:v>
+      </x:c>
+      <x:c r="C230" s="3" t="str"/>
+      <x:c r="D230" s="3" t="str"/>
+      <x:c r="E230" s="3" t="str"/>
+      <x:c r="F230" s="3" t="str"/>
+      <x:c r="G230" s="3" t="str">
+        <x:v>先说明低氧细胞与组织培养用途，再展示操作口、两端气闸和双人布局；随后列环境控制、状态显示、记录选配、规格和安装资料，最后提供更大型号与咨询入口。</x:v>
+      </x:c>
+      <x:c r="H230" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231" ht="59" customHeight="1">
+      <x:c r="A231" s="3" t="str">
+        <x:v>竞品分析</x:v>
+      </x:c>
+      <x:c r="B231" s="3" t="str">
+        <x:v>DWS-H55 · PUN可采用的写法</x:v>
+      </x:c>
+      <x:c r="C231" s="3" t="str"/>
+      <x:c r="D231" s="3" t="str"/>
+      <x:c r="E231" s="3" t="str"/>
+      <x:c r="F231" s="3" t="str"/>
+      <x:c r="G231" s="3" t="str">
+        <x:v>先用一张表区分厌氧与低氧版本。低氧版分别说明微需氧微生物操作培养、细胞与组织低氧培养，配实际操作、物料转移、配置表和测试记录；具体参数与资料对应到版本和型号。</x:v>
+      </x:c>
+      <x:c r="H231" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232" ht="48" customHeight="1">
+      <x:c r="A232" s="3" t="str">
+        <x:v>竞品分析</x:v>
+      </x:c>
+      <x:c r="B232" s="3" t="str">
+        <x:v>DWS-H55 · 月自然流量估值</x:v>
+      </x:c>
+      <x:c r="C232" s="3" t="str"/>
+      <x:c r="D232" s="3" t="str"/>
+      <x:c r="E232" s="3" t="str"/>
+      <x:c r="F232" s="3" t="str"/>
+      <x:c r="G232" s="3" t="str">
+        <x:v>36；供应商估值含型号歧义词，不代表低氧品类需求</x:v>
+      </x:c>
+      <x:c r="H232" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233" ht="48" customHeight="1">
+      <x:c r="A233" s="3" t="str">
+        <x:v>竞品分析</x:v>
+      </x:c>
+      <x:c r="B233" s="3" t="str">
+        <x:v>DWS-H55 · 域内排名</x:v>
+      </x:c>
+      <x:c r="C233" s="3" t="str"/>
+      <x:c r="D233" s="3" t="str"/>
+      <x:c r="E233" s="3" t="str"/>
+      <x:c r="F233" s="3" t="str"/>
+      <x:c r="G233" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H233" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234" ht="48" customHeight="1">
+      <x:c r="A234" s="3" t="str">
+        <x:v>竞品分析</x:v>
+      </x:c>
+      <x:c r="B234" s="3" t="str">
+        <x:v>DWS-H55 · 网页地址</x:v>
+      </x:c>
+      <x:c r="C234" s="3" t="str"/>
+      <x:c r="D234" s="3" t="str"/>
+      <x:c r="E234" s="3" t="str"/>
+      <x:c r="F234" s="3" t="str"/>
+      <x:c r="G234" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+      <x:c r="H234" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235" ht="48" customHeight="1">
+      <x:c r="A235" s="3" t="str">
+        <x:v>竞品分析</x:v>
+      </x:c>
+      <x:c r="B235" s="3" t="str">
+        <x:v>DWS-H55 · 搜索标题</x:v>
+      </x:c>
+      <x:c r="C235" s="3" t="str"/>
+      <x:c r="D235" s="3" t="str"/>
+      <x:c r="E235" s="3" t="str"/>
+      <x:c r="F235" s="3" t="str"/>
+      <x:c r="G235" s="3" t="str">
+        <x:v>Whitley H55 Hypoxystation</x:v>
+      </x:c>
+      <x:c r="H235" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236" ht="48" customHeight="1">
+      <x:c r="A236" s="3" t="str">
+        <x:v>竞品分析</x:v>
+      </x:c>
+      <x:c r="B236" s="3" t="str">
+        <x:v>DWS-H55 · 搜索摘要</x:v>
+      </x:c>
+      <x:c r="C236" s="3" t="str"/>
+      <x:c r="D236" s="3" t="str"/>
+      <x:c r="E236" s="3" t="str"/>
+      <x:c r="F236" s="3" t="str"/>
+      <x:c r="G236" s="3" t="str">
+        <x:v>保存的HTML中未检测到</x:v>
+      </x:c>
+      <x:c r="H236" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237" ht="48" customHeight="1">
+      <x:c r="A237" s="3" t="str">
+        <x:v>竞品分析</x:v>
+      </x:c>
+      <x:c r="B237" s="3" t="str">
+        <x:v>DWS-H55 · 标准地址 canonical</x:v>
+      </x:c>
+      <x:c r="C237" s="3" t="str"/>
+      <x:c r="D237" s="3" t="str"/>
+      <x:c r="E237" s="3" t="str"/>
+      <x:c r="F237" s="3" t="str"/>
+      <x:c r="G237" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+      <x:c r="H237" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238" ht="48" customHeight="1">
+      <x:c r="A238" s="3" t="str">
+        <x:v>竞品分析</x:v>
+      </x:c>
+      <x:c r="B238" s="3" t="str">
+        <x:v>DWS-H55 · 索引指令 robots</x:v>
+      </x:c>
+      <x:c r="C238" s="3" t="str"/>
+      <x:c r="D238" s="3" t="str"/>
+      <x:c r="E238" s="3" t="str"/>
+      <x:c r="F238" s="3" t="str"/>
+      <x:c r="G238" s="3" t="str">
+        <x:v>保存的HTML中未检测到</x:v>
+      </x:c>
+      <x:c r="H238" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239" ht="48" customHeight="1">
+      <x:c r="A239" s="3" t="str">
+        <x:v>竞品分析</x:v>
+      </x:c>
+      <x:c r="B239" s="3" t="str">
+        <x:v>DWS-H55 · 社交分享 og:site_name</x:v>
+      </x:c>
+      <x:c r="C239" s="3" t="str"/>
+      <x:c r="D239" s="3" t="str"/>
+      <x:c r="E239" s="3" t="str"/>
+      <x:c r="F239" s="3" t="str"/>
+      <x:c r="G239" s="3" t="str">
+        <x:v>Don Whitley Scientific</x:v>
+      </x:c>
+      <x:c r="H239" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240" ht="48" customHeight="1">
+      <x:c r="A240" s="3" t="str">
+        <x:v>竞品分析</x:v>
+      </x:c>
+      <x:c r="B240" s="3" t="str">
+        <x:v>DWS-H55 · 社交分享 og:title</x:v>
+      </x:c>
+      <x:c r="C240" s="3" t="str"/>
+      <x:c r="D240" s="3" t="str"/>
+      <x:c r="E240" s="3" t="str"/>
+      <x:c r="F240" s="3" t="str"/>
+      <x:c r="G240" s="3" t="str">
+        <x:v>Whitley H55 Hypoxystation</x:v>
+      </x:c>
+      <x:c r="H240" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241" ht="48" customHeight="1">
+      <x:c r="A241" s="3" t="str">
+        <x:v>竞品分析</x:v>
+      </x:c>
+      <x:c r="B241" s="3" t="str">
+        <x:v>DWS-H55 · 社交分享 og:type</x:v>
+      </x:c>
+      <x:c r="C241" s="3" t="str"/>
+      <x:c r="D241" s="3" t="str"/>
+      <x:c r="E241" s="3" t="str"/>
+      <x:c r="F241" s="3" t="str"/>
+      <x:c r="G241" s="3" t="str">
+        <x:v>website</x:v>
+      </x:c>
+      <x:c r="H241" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242" ht="48" customHeight="1">
+      <x:c r="A242" s="3" t="str">
+        <x:v>竞品分析</x:v>
+      </x:c>
+      <x:c r="B242" s="3" t="str">
+        <x:v>DWS-H55 · 社交分享 og:url</x:v>
+      </x:c>
+      <x:c r="C242" s="3" t="str"/>
+      <x:c r="D242" s="3" t="str"/>
+      <x:c r="E242" s="3" t="str"/>
+      <x:c r="F242" s="3" t="str"/>
+      <x:c r="G242" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+      <x:c r="H242" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243" ht="48" customHeight="1">
+      <x:c r="A243" s="3" t="str">
+        <x:v>竞品分析</x:v>
+      </x:c>
+      <x:c r="B243" s="3" t="str">
+        <x:v>DWS-H55 · 社交分享 twitter:card</x:v>
+      </x:c>
+      <x:c r="C243" s="3" t="str"/>
+      <x:c r="D243" s="3" t="str"/>
+      <x:c r="E243" s="3" t="str"/>
+      <x:c r="F243" s="3" t="str"/>
+      <x:c r="G243" s="3" t="str">
+        <x:v>summary</x:v>
+      </x:c>
+      <x:c r="H243" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244" ht="48" customHeight="1">
+      <x:c r="A244" s="3" t="str">
+        <x:v>竞品分析</x:v>
+      </x:c>
+      <x:c r="B244" s="3" t="str">
+        <x:v>DWS-H55 · 社交分享 twitter:title</x:v>
+      </x:c>
+      <x:c r="C244" s="3" t="str"/>
+      <x:c r="D244" s="3" t="str"/>
+      <x:c r="E244" s="3" t="str"/>
+      <x:c r="F244" s="3" t="str"/>
+      <x:c r="G244" s="3" t="str">
+        <x:v>Whitley H55 Hypoxystation</x:v>
+      </x:c>
+      <x:c r="H244" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245" ht="48" customHeight="1">
+      <x:c r="A245" s="3" t="str">
+        <x:v>竞品分析</x:v>
+      </x:c>
+      <x:c r="B245" s="3" t="str">
+        <x:v>DWS-H55 · 结构化数据类型</x:v>
+      </x:c>
+      <x:c r="C245" s="3" t="str"/>
+      <x:c r="D245" s="3" t="str"/>
+      <x:c r="E245" s="3" t="str"/>
+      <x:c r="F245" s="3" t="str"/>
+      <x:c r="G245" s="3" t="str">
+        <x:v>BreadcrumbList</x:v>
+      </x:c>
+      <x:c r="H245" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="246" ht="149" customHeight="1">
+      <x:c r="A246" s="3" t="str">
+        <x:v>竞品分析</x:v>
+      </x:c>
+      <x:c r="B246" s="3" t="str">
+        <x:v>DWS-H55 · 可以补充的内容</x:v>
+      </x:c>
+      <x:c r="C246" s="3" t="str"/>
+      <x:c r="D246" s="3" t="str"/>
+      <x:c r="E246" s="3" t="str"/>
+      <x:c r="F246" s="3" t="str"/>
+      <x:c r="G246" s="3" t="str">
+        <x:v>概述写每个气闸可容纳4块96孔板，规格表写最多44块96孔板，两处数字不一致。 PUN按版本列气闸可用尺寸、板型、装载数量和布局图，让正文、规格表与下载文件使用同一组经确认数据。
+概述把连续培养环境与减少细胞应激、改善细胞系联系起来，但同一段未列比较条件、样本或结果图。 如PUN要说明培养收益，配实际样本、实验条件、比较方法和结果；同时将环境控制性能与生物学结果分开呈现。
+页面分别列状态显示、数据记录和氧浓度曲线选配，阅读概述时仍需对照规格与选项才能完成配置判断。 PUN用一张版本配置表区分标准配置与选配，并给出实际记录样张和安装文件，帮助技术与采购共同确认需求。</x:v>
+      </x:c>
+      <x:c r="H246" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="247" ht="48" customHeight="1">
+      <x:c r="A247" s="3" t="str">
+        <x:v>竞品分析</x:v>
+      </x:c>
+      <x:c r="B247" s="3" t="str">
+        <x:v>DWS-H55 · 产品事实边界</x:v>
+      </x:c>
+      <x:c r="C247" s="3" t="str"/>
+      <x:c r="D247" s="3" t="str"/>
+      <x:c r="E247" s="3" t="str"/>
+      <x:c r="F247" s="3" t="str"/>
+      <x:c r="G247" s="3" t="str">
+        <x:v>H55的氧浓度、CO2、温湿度、容量、气闸周期、端口、记录功能、HEPA、专利、细胞表现和服务均属于DWS产品陈述；PUN各版本的功能、数值及适用条件使用对应型号资料。</x:v>
+      </x:c>
+      <x:c r="H247" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="248" ht="89" customHeight="1">
+      <x:c r="A248" s="3" t="str">
+        <x:v>竞品关键词与采用机会</x:v>
+      </x:c>
+      <x:c r="B248" s="3" t="str">
+        <x:v>DWS-H55 · ★ Whitley H55 Hypoxystation</x:v>
+      </x:c>
+      <x:c r="C248" s="3" t="str"/>
+      <x:c r="D248" s="3" t="str"/>
+      <x:c r="E248" s="3" t="str"/>
+      <x:c r="F248" s="3" t="str"/>
+      <x:c r="G248" s="3" t="str">
+        <x:v>月量 未取得；KD 未取得；SD 未取得；CPC $未取得；PD 未取得；广告竞争 未取得；PT第3位情景 未取得；第10位情景 未取得
+页面主题候选；竞争品牌导航
+不采纳。DWS品牌型号导航词。保留页面研究，不作为PUN主词，不按该词新增页面。
+参数更新 未取得；历史末月 未取得；读取 2026-10-29</x:v>
+      </x:c>
+      <x:c r="H248" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="249" ht="104" customHeight="1">
+      <x:c r="A249" s="3" t="str">
+        <x:v>竞品关键词与采用机会</x:v>
+      </x:c>
+      <x:c r="B249" s="3" t="str">
+        <x:v>DWS-H55 · ★★★★★ hypoxia chamber</x:v>
+      </x:c>
+      <x:c r="C249" s="3" t="str"/>
+      <x:c r="D249" s="3" t="str"/>
+      <x:c r="E249" s="3" t="str"/>
+      <x:c r="F249" s="3" t="str"/>
+      <x:c r="G249" s="3" t="str">
+        <x:v>月量 1000；KD 0；SD 36；CPC $7.43；PD 61；广告竞争 0.61；PT第3位情景 78.8；第10位情景 10.7
+基于页面任务的主题候选；独立关键词概览参数；实验室低氧设备采购与应用比较
+低氧版本说明及低氧选型入口候选。词量1000，样本为实验室低氧线索，仍混有论文、便携培养舱和培养箱。先说明工作站形态、适用任务及与其他设备的差别。
+参数更新 未取得；历史末月 202608；读取 2026-10-29</x:v>
+      </x:c>
+      <x:c r="H249" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="250" ht="104" customHeight="1">
+      <x:c r="A250" s="3" t="str">
+        <x:v>竞品关键词与采用机会</x:v>
+      </x:c>
+      <x:c r="B250" s="3" t="str">
+        <x:v>DWS-H55 · ★★★★★ hypoxia workstation</x:v>
+      </x:c>
+      <x:c r="C250" s="3" t="str"/>
+      <x:c r="D250" s="3" t="str"/>
+      <x:c r="E250" s="3" t="str"/>
+      <x:c r="F250" s="3" t="str"/>
+      <x:c r="G250" s="3" t="str">
+        <x:v>月量 20；KD 4；SD 29；CPC $0；PD 35；广告竞争 0.35；PT第3位情景 1.6；第10位情景 0.2
+基于页面任务的主题候选；独立关键词概览参数；低氧工作站采购评估
+版本选择和低氧实验任务H2/H3。词量20但设备类别较明确；以低氧版支持的任务、操作方式、配置和受控资料回应采购评估。两种写法不相加。
+参数更新 未取得；历史末月 202609；读取 2026-10-29</x:v>
+      </x:c>
+      <x:c r="H250" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="251" ht="104" customHeight="1">
+      <x:c r="A251" s="3" t="str">
+        <x:v>竞品关键词与采用机会</x:v>
+      </x:c>
+      <x:c r="B251" s="3" t="str">
+        <x:v>DWS-H55 · ★★★★★ hypoxic workstation</x:v>
+      </x:c>
+      <x:c r="C251" s="3" t="str"/>
+      <x:c r="D251" s="3" t="str"/>
+      <x:c r="E251" s="3" t="str"/>
+      <x:c r="F251" s="3" t="str"/>
+      <x:c r="G251" s="3" t="str">
+        <x:v>月量 20；KD 6；SD 29；CPC $0；PD 35；广告竞争 0.35；PT第3位情景 1.6；第10位情景 0.2
+基于页面任务的主题候选；独立关键词概览参数；低氧工作站采购评估
+版本选择和低氧实验任务H2/H3。词量20但设备类别较明确；以低氧版支持的任务、操作方式、配置和受控资料回应采购评估。两种写法不相加。
+参数更新 未取得；历史末月 202609；读取 2026-10-29</x:v>
+      </x:c>
+      <x:c r="H251" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="252" ht="119" customHeight="1">
+      <x:c r="A252" s="3" t="str">
+        <x:v>竞品关键词与采用机会</x:v>
+      </x:c>
+      <x:c r="B252" s="3" t="str">
+        <x:v>DWS-H55 · ★★★★ hypoxia chamber for cell culture</x:v>
+      </x:c>
+      <x:c r="C252" s="3" t="str"/>
+      <x:c r="D252" s="3" t="str"/>
+      <x:c r="E252" s="3" t="str"/>
+      <x:c r="F252" s="3" t="str"/>
+      <x:c r="G252" s="3" t="str">
+        <x:v>月量 140；KD 0；SD 29；CPC $8.91；PD 91；广告竞争 0.91；PT第3位情景 11.0；第10位情景 1.5
+基于页面任务的主题候选；独立关键词概览参数；低氧细胞与组织任务、设备形态及条件比较
+细胞/组织应用、工作站与培养舱区别H3。低氧细胞培养任务相关，但结果有放入现有培养箱的小舱及低氧培养箱，需按实际设备形态和操作条件说明匹配。
+参数更新 未取得；历史末月 202607；读取 2026-10-29</x:v>
+      </x:c>
+      <x:c r="H252" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="253" ht="119" customHeight="1">
+      <x:c r="A253" s="3" t="str">
+        <x:v>竞品关键词与采用机会</x:v>
+      </x:c>
+      <x:c r="B253" s="3" t="str">
+        <x:v>DWS-H55 · ★★★★ hypoxic chamber cell culture</x:v>
+      </x:c>
+      <x:c r="C253" s="3" t="str"/>
+      <x:c r="D253" s="3" t="str"/>
+      <x:c r="E253" s="3" t="str"/>
+      <x:c r="F253" s="3" t="str"/>
+      <x:c r="G253" s="3" t="str">
+        <x:v>月量 50；KD 0；SD 20；CPC $8.04；PD 53；广告竞争 0.53；PT第3位情景 3.9；第10位情景 0.5
+基于页面任务的主题候选；独立关键词概览参数；低氧细胞与组织任务、设备形态及条件比较
+细胞/组织应用、工作站与培养舱区别H3。低氧细胞培养任务相关，但结果有放入现有培养箱的小舱及低氧培养箱，需按实际设备形态和操作条件说明匹配。
+参数更新 2025-11-24；历史末月 未取得；读取 2026-10-29</x:v>
+      </x:c>
+      <x:c r="H253" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="254" ht="119" customHeight="1">
+      <x:c r="A254" s="3" t="str">
+        <x:v>竞品关键词与采用机会</x:v>
+      </x:c>
+      <x:c r="B254" s="3" t="str">
+        <x:v>DWS-H55 · ★★★★ hypoxic chamber for cell culture</x:v>
+      </x:c>
+      <x:c r="C254" s="3" t="str"/>
+      <x:c r="D254" s="3" t="str"/>
+      <x:c r="E254" s="3" t="str"/>
+      <x:c r="F254" s="3" t="str"/>
+      <x:c r="G254" s="3" t="str">
+        <x:v>月量 110；KD 0；SD 35；CPC $7.5；PD 86；广告竞争 0.86；PT第3位情景 8.7；第10位情景 1.2
+基于页面任务的主题候选；独立关键词概览参数；低氧细胞与组织任务、设备形态及条件比较
+细胞/组织应用、工作站与培养舱区别H3。低氧细胞培养任务相关，但结果有放入现有培养箱的小舱及低氧培养箱，需按实际设备形态和操作条件说明匹配。
+参数更新 2026-09-20；历史末月 未取得；读取 2026-10-29</x:v>
+      </x:c>
+      <x:c r="H254" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="255" ht="104" customHeight="1">
+      <x:c r="A255" s="3" t="str">
+        <x:v>竞品关键词与采用机会</x:v>
+      </x:c>
+      <x:c r="B255" s="3" t="str">
+        <x:v>DWS-H55 · ★★★★ hypoxia glove box</x:v>
+      </x:c>
+      <x:c r="C255" s="3" t="str"/>
+      <x:c r="D255" s="3" t="str"/>
+      <x:c r="E255" s="3" t="str"/>
+      <x:c r="F255" s="3" t="str"/>
+      <x:c r="G255" s="3" t="str">
+        <x:v>月量 10；KD 0；SD 13；CPC $0；PD 1；广告竞争 0；PT第3位情景 0.8；第10位情景 0.1
+基于页面任务的主题候选；独立关键词概览参数；操作方式与设备采购
+操作空间、操作口及转移条件。在设备操作形式上较具体；使用PUN实物、装载、转移和控制资料说明，不据词名推断功能。
+参数更新 未取得；历史末月 202608；读取 2026-10-29</x:v>
+      </x:c>
+      <x:c r="H255" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="256" ht="104" customHeight="1">
+      <x:c r="A256" s="3" t="str">
+        <x:v>竞品关键词与采用机会</x:v>
+      </x:c>
+      <x:c r="B256" s="3" t="str">
+        <x:v>DWS-H55 · ★★★★ hypoxic glove box</x:v>
+      </x:c>
+      <x:c r="C256" s="3" t="str"/>
+      <x:c r="D256" s="3" t="str"/>
+      <x:c r="E256" s="3" t="str"/>
+      <x:c r="F256" s="3" t="str"/>
+      <x:c r="G256" s="3" t="str">
+        <x:v>月量 10；KD 0；SD 13；CPC $0；PD 1；广告竞争 0；PT第3位情景 0.8；第10位情景 0.1
+基于页面任务的主题候选；独立关键词概览参数；操作方式与设备采购
+操作空间、操作口及转移条件。在设备操作形式上较具体；使用PUN实物、装载、转移和控制资料说明，不据词名推断功能。
+参数更新 未取得；历史末月 202608；读取 2026-10-29</x:v>
+      </x:c>
+      <x:c r="H256" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="257" ht="119" customHeight="1">
+      <x:c r="A257" s="3" t="str">
+        <x:v>竞品关键词与采用机会</x:v>
+      </x:c>
+      <x:c r="B257" s="3" t="str">
+        <x:v>DWS-H55 · ★★★ low oxygen chamber</x:v>
+      </x:c>
+      <x:c r="C257" s="3" t="str"/>
+      <x:c r="D257" s="3" t="str"/>
+      <x:c r="E257" s="3" t="str"/>
+      <x:c r="F257" s="3" t="str"/>
+      <x:c r="G257" s="3" t="str">
+        <x:v>月量 10；KD 未取得；SD 41；CPC $0；PD 90；广告竞争 0.9；PT第3位情景 0.8；第10位情景 0.1
+基于页面任务的主题候选；独立关键词概览参数；低氧细胞与组织任务、设备形态及条件比较
+低氧版定义和常见问题。词量10，表达较宽；作为实验室低氧说明的同题表达，页面先限定设备形态和使用者。
+参数更新 未取得；历史末月 202601；读取 2026-10-29</x:v>
+      </x:c>
+      <x:c r="H257" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="258" ht="119" customHeight="1">
+      <x:c r="A258" s="3" t="str">
+        <x:v>竞品关键词与采用机会</x:v>
+      </x:c>
+      <x:c r="B258" s="3" t="str">
+        <x:v>DWS-H55 · ★★★ hypoxic workstation for cell culture</x:v>
+      </x:c>
+      <x:c r="C258" s="3" t="str"/>
+      <x:c r="D258" s="3" t="str"/>
+      <x:c r="E258" s="3" t="str"/>
+      <x:c r="F258" s="3" t="str"/>
+      <x:c r="G258" s="3" t="str">
+        <x:v>月量 0；KD 未取得；SD 4；CPC $0；PD 1；广告竞争 0；PT第3位情景 0；第10位情景 0
+基于页面任务的主题候选；独立关键词概览参数；低氧细胞与组织任务、设备形态及条件比较
+对应任务H2/H3自然覆盖。供应商对该精确表达返回0且未提供历史序列；保留为同题用语，不量化为已证实规模，不据此新增URL。
+参数更新 未取得；历史末月 未取得；读取 2026-10-29</x:v>
+      </x:c>
+      <x:c r="H258" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="259" ht="119" customHeight="1">
+      <x:c r="A259" s="3" t="str">
+        <x:v>竞品关键词与采用机会</x:v>
+      </x:c>
+      <x:c r="B259" s="3" t="str">
+        <x:v>DWS-H55 · ★★★ hypoxic workstations</x:v>
+      </x:c>
+      <x:c r="C259" s="3" t="str"/>
+      <x:c r="D259" s="3" t="str"/>
+      <x:c r="E259" s="3" t="str"/>
+      <x:c r="F259" s="3" t="str"/>
+      <x:c r="G259" s="3" t="str">
+        <x:v>月量 0；KD 未取得；SD 17；CPC $0；PD 1；广告竞争 0；PT第3位情景 0；第10位情景 0
+基于页面任务的主题候选；独立关键词概览参数；低氧细胞与组织任务、设备形态及条件比较
+对应任务H2/H3自然覆盖。供应商对该精确表达返回0且未提供历史序列；保留为同题用语，不量化为已证实规模，不据此新增URL。
+参数更新 未取得；历史末月 未取得；读取 2026-10-29</x:v>
+      </x:c>
+      <x:c r="H259" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="260" ht="119" customHeight="1">
+      <x:c r="A260" s="3" t="str">
+        <x:v>竞品关键词与采用机会</x:v>
+      </x:c>
+      <x:c r="B260" s="3" t="str">
+        <x:v>DWS-H55 · ★★★ low oxygen workstation</x:v>
+      </x:c>
+      <x:c r="C260" s="3" t="str"/>
+      <x:c r="D260" s="3" t="str"/>
+      <x:c r="E260" s="3" t="str"/>
+      <x:c r="F260" s="3" t="str"/>
+      <x:c r="G260" s="3" t="str">
+        <x:v>月量 0；KD 未取得；SD 12；CPC $0；PD 1；广告竞争 0；PT第3位情景 0；第10位情景 0
+基于页面任务的主题候选；独立关键词概览参数；低氧细胞与组织任务、设备形态及条件比较
+对应任务H2/H3自然覆盖。供应商对该精确表达返回0且未提供历史序列；保留为同题用语，不量化为已证实规模，不据此新增URL。
+参数更新 未取得；历史末月 未取得；读取 2026-10-29</x:v>
+      </x:c>
+      <x:c r="H260" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="261" ht="119" customHeight="1">
+      <x:c r="A261" s="3" t="str">
+        <x:v>竞品关键词与采用机会</x:v>
+      </x:c>
+      <x:c r="B261" s="3" t="str">
+        <x:v>DWS-H55 · ★★ controlled atmosphere workstation</x:v>
+      </x:c>
+      <x:c r="C261" s="3" t="str"/>
+      <x:c r="D261" s="3" t="str"/>
+      <x:c r="E261" s="3" t="str"/>
+      <x:c r="F261" s="3" t="str"/>
+      <x:c r="G261" s="3" t="str">
+        <x:v>月量 0；KD 未取得；SD 12；CPC $0；PD 1；广告竞争 0；PT第3位情景 0；第10位情景 0
+基于页面任务的主题候选；独立关键词概览参数；低氧细胞与组织任务、设备形态及条件比较
+介绍中解释设备类别。范围广于厌氧和低氧；以明确版本与任务限定含义，暂不按这一泛称另建采购页。
+参数更新 未取得；历史末月 未取得；读取 2026-10-29</x:v>
+      </x:c>
+      <x:c r="H261" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="262" ht="104" customHeight="1">
+      <x:c r="A262" s="3" t="str">
+        <x:v>竞品关键词与采用机会</x:v>
+      </x:c>
+      <x:c r="B262" s="3" t="str">
+        <x:v>DWS-H55 · ★★ hypoxia incubator chamber</x:v>
+      </x:c>
+      <x:c r="C262" s="3" t="str"/>
+      <x:c r="D262" s="3" t="str"/>
+      <x:c r="E262" s="3" t="str"/>
+      <x:c r="F262" s="3" t="str"/>
+      <x:c r="G262" s="3" t="str">
+        <x:v>月量 40；KD 0；SD 18；CPC $2.56；PD 93；广告竞争 0.93；PT第3位情景 3.2；第10位情景 0.4
+基于页面任务的主题候选；独立关键词概览参数；低氧设备形态比较
+设备类型比较和适用条件。常指放进培养箱的便携密闭小舱。把设备区别讲清，不能直接当作PUN整机工作站的主要采购词。
+参数更新 未取得；历史末月 202609；读取 2026-10-29</x:v>
+      </x:c>
+      <x:c r="H262" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="263" ht="119" customHeight="1">
+      <x:c r="A263" s="3" t="str">
+        <x:v>竞品关键词与采用机会</x:v>
+      </x:c>
+      <x:c r="B263" s="3" t="str">
+        <x:v>DWS-H55 · ★★ hypoxic chamber</x:v>
+      </x:c>
+      <x:c r="C263" s="3" t="str"/>
+      <x:c r="D263" s="3" t="str"/>
+      <x:c r="E263" s="3" t="str"/>
+      <x:c r="F263" s="3" t="str"/>
+      <x:c r="G263" s="3" t="str">
+        <x:v>月量 1000；KD 0；SD 34；CPC $7.43；PD 61；广告竞争 0.61；PT第3位情景 78.8；第10位情景 10.7
+基于页面任务的主题候选；独立关键词概览参数；以人体海拔训练为主的混合意图；仅限定实验室语境
+实验室限定语中的自然别名。词量1000，但当前10条自然样本以人体训练、海拔及运动场景为主；不把该词全部需求计为PUN机会。
+参数更新 2026-09-07；历史末月 未取得；读取 2026-10-29</x:v>
+      </x:c>
+      <x:c r="H263" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="264" ht="119" customHeight="1">
+      <x:c r="A264" s="3" t="str">
+        <x:v>竞品关键词与采用机会</x:v>
+      </x:c>
+      <x:c r="B264" s="3" t="str">
+        <x:v>DWS-H55 · ★★ what is a hypoxic chamber</x:v>
+      </x:c>
+      <x:c r="C264" s="3" t="str"/>
+      <x:c r="D264" s="3" t="str"/>
+      <x:c r="E264" s="3" t="str"/>
+      <x:c r="F264" s="3" t="str"/>
+      <x:c r="G264" s="3" t="str">
+        <x:v>月量 110；KD 1；SD 37；CPC $0；PD 1；广告竞争 0.01；PT第3位情景 8.7；第10位情景 1.2
+基于页面任务的主题候选；独立关键词概览参数；低氧细胞与组织任务、设备形态及条件比较
+FAQ，先区分实验室与人体训练语境。定义词混有训练理解任务；用一句直接说明实验室低氧工作站并链接相应任务，暂不单建泛定义页。
+参数更新 2026-09-19；历史末月 未取得；读取 2026-10-29</x:v>
+      </x:c>
+      <x:c r="H264" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="265" ht="48" customHeight="1">
+      <x:c r="A265" s="3" t="str">
+        <x:v>竞品标题</x:v>
+      </x:c>
+      <x:c r="B265" s="3" t="str">
+        <x:v>DWS-H55 · H1</x:v>
+      </x:c>
+      <x:c r="C265" s="3" t="str">
+        <x:v>Whitley H55 Hypoxystation</x:v>
+      </x:c>
+      <x:c r="D265" s="3" t="str">
+        <x:v>Whitley H55 低氧工作站</x:v>
+      </x:c>
+      <x:c r="E265" s="3" t="str"/>
+      <x:c r="F265" s="3" t="str"/>
+      <x:c r="G265" s="3" t="str"/>
+      <x:c r="H265" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="266" ht="48" customHeight="1">
+      <x:c r="A266" s="3" t="str">
+        <x:v>竞品标题</x:v>
+      </x:c>
+      <x:c r="B266" s="3" t="str">
+        <x:v>DWS-H55 · H2</x:v>
+      </x:c>
+      <x:c r="C266" s="3" t="str">
+        <x:v>Hypoxystation with two airlocks, ideal for two people working side by side</x:v>
+      </x:c>
+      <x:c r="D266" s="3" t="str">
+        <x:v>配有两个传递舱、适合两人并排操作的低氧工作站</x:v>
+      </x:c>
+      <x:c r="E266" s="3" t="str"/>
+      <x:c r="F266" s="3" t="str"/>
+      <x:c r="G266" s="3" t="str"/>
+      <x:c r="H266" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="267" ht="74" customHeight="1">
+      <x:c r="A267" s="3" t="str">
+        <x:v>正文示范</x:v>
+      </x:c>
+      <x:c r="B267" s="3" t="str">
+        <x:v>DWS-H55 · 示范1 · Whitley H55 Hypoxystation</x:v>
+      </x:c>
+      <x:c r="C267" s="3" t="str">
+        <x:v>The Whitley H55 provides a low-oxygen workspace for cell and tissue culture, with controls for oxygen, carbon dioxide and humidity. Researchers can work with cultures inside the controlled chamber environment.</x:v>
+      </x:c>
+      <x:c r="D267" s="3" t="str">
+        <x:v>Whitley H55为细胞与组织培养提供低氧工作空间，可控制氧气、二氧化碳和湿度。研究人员可在腔体内的受控环境中操作培养物。</x:v>
+      </x:c>
+      <x:c r="E267" s="3" t="str"/>
+      <x:c r="F267" s="3" t="str"/>
+      <x:c r="G267" s="3" t="str"/>
+      <x:c r="H267" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="268" ht="74" customHeight="1">
+      <x:c r="A268" s="3" t="str">
+        <x:v>正文示范</x:v>
+      </x:c>
+      <x:c r="B268" s="3" t="str">
+        <x:v>DWS-H55 · 示范2 · Hypoxystation with two airlocks, ideal for two people working side by side</x:v>
+      </x:c>
+      <x:c r="C268" s="3" t="str">
+        <x:v>The H55 has four sleeved access ports and an airlock at each end. Two operators can work side by side, while the two airlocks provide routes for moving materials into and out of the workspace.</x:v>
+      </x:c>
+      <x:c r="D268" s="3" t="str">
+        <x:v>H55配有四个带袖套的操作口，两端各有一个气闸。两名操作人员可以并排工作，物料可通过两端气闸进出工作空间。</x:v>
+      </x:c>
+      <x:c r="E268" s="3" t="str"/>
+      <x:c r="F268" s="3" t="str"/>
+      <x:c r="G268" s="3" t="str"/>
+      <x:c r="H268" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="269" ht="74" customHeight="1">
+      <x:c r="A269" s="3" t="str">
+        <x:v>正文示范</x:v>
+      </x:c>
+      <x:c r="B269" s="3" t="str">
+        <x:v>DWS-H55 · 示范3 · Whitley H55 Hypoxystation</x:v>
+      </x:c>
+      <x:c r="C269" s="3" t="str">
+        <x:v>A touchscreen displays oxygen, carbon dioxide, temperature, humidity and airlock status. Data logging and oxygen profiling are available as options, so these recording functions can be specified alongside the workstation configuration.</x:v>
+      </x:c>
+      <x:c r="D269" s="3" t="str">
+        <x:v>触摸屏显示氧气、二氧化碳、温度、湿度和气闸状态。数据记录与氧浓度曲线属于可选功能，客户可在确定工作站配置时一并选择。</x:v>
+      </x:c>
+      <x:c r="E269" s="3" t="str"/>
+      <x:c r="F269" s="3" t="str"/>
+      <x:c r="G269" s="3" t="str"/>
+      <x:c r="H269" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="270" ht="48" customHeight="1">
+      <x:c r="A270" s="3" t="str">
+        <x:v>竞品媒体</x:v>
+      </x:c>
+      <x:c r="B270" s="3" t="str">
+        <x:v>DWS-H55 · 图片</x:v>
+      </x:c>
+      <x:c r="C270" s="3" t="str">
+        <x:v>Whitley H55 Hypoxystation image</x:v>
+      </x:c>
+      <x:c r="D270" s="3" t="str"/>
+      <x:c r="E270" s="3" t="str"/>
+      <x:c r="F270" s="3" t="str"/>
+      <x:c r="G270" s="3" t="str">
+        <x:v>https://www.dwscientific.com/storage/app/uploads/public/f33/bd4/710/700_500_0_0_auto/6763e2efc0167766237618.webp</x:v>
+      </x:c>
+      <x:c r="H270" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="271" ht="48" customHeight="1">
+      <x:c r="A271" s="3" t="str">
+        <x:v>竞品媒体</x:v>
+      </x:c>
+      <x:c r="B271" s="3" t="str">
+        <x:v>DWS-H55 · 图片</x:v>
+      </x:c>
+      <x:c r="C271" s="3" t="str">
+        <x:v>6763e2efc0167766237618.webp</x:v>
+      </x:c>
+      <x:c r="D271" s="3" t="str"/>
+      <x:c r="E271" s="3" t="str"/>
+      <x:c r="F271" s="3" t="str"/>
+      <x:c r="G271" s="3" t="str">
+        <x:v>https://www.dwscientific.com/storage/app/uploads/public/f33/bd4/710/1200_857_0_0_auto/6763e2efc0167766237618.webp</x:v>
+      </x:c>
+      <x:c r="H271" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272" ht="48" customHeight="1">
+      <x:c r="A272" s="3" t="str">
+        <x:v>竞品媒体</x:v>
+      </x:c>
+      <x:c r="B272" s="3" t="str">
+        <x:v>DWS-H55 · 图片</x:v>
+      </x:c>
+      <x:c r="C272" s="3" t="str">
+        <x:v>Whitley H95 Hypoxystation</x:v>
+      </x:c>
+      <x:c r="D272" s="3" t="str"/>
+      <x:c r="E272" s="3" t="str"/>
+      <x:c r="F272" s="3" t="str"/>
+      <x:c r="G272" s="3" t="str">
+        <x:v>https://www.dwscientific.com/storage/app/uploads/public/b09/269/fe6/387__0_0_auto/5dad8c1c613a4666305178.webp</x:v>
+      </x:c>
+      <x:c r="H272" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="273" ht="48" customHeight="1">
+      <x:c r="A273" s="3" t="str">
+        <x:v>竞品媒体</x:v>
+      </x:c>
+      <x:c r="B273" s="3" t="str">
+        <x:v>DWS-H55 · 视频</x:v>
+      </x:c>
+      <x:c r="C273" s="3" t="str">
+        <x:v>Replicate growth conditions and mimic different climates with a Whitley Hypoxystation</x:v>
+      </x:c>
+      <x:c r="D273" s="3" t="str">
+        <x:v>使用Whitley低氧工作站复现生长条件并模拟不同环境</x:v>
+      </x:c>
+      <x:c r="E273" s="3" t="str"/>
+      <x:c r="F273" s="3" t="str"/>
+      <x:c r="G273" s="3" t="str">
+        <x:v>https://www.youtube.com/watch?v=tsCCU2ovXYA</x:v>
+      </x:c>
+      <x:c r="H273" s="3" t="str">
+        <x:v>https://www.dwscientific.com/whitley-hypoxic-workstations/whitley-h55-hypoxystation</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13081,7 +13880,7 @@
       </x:c>
       <x:c r="B3" s="3"/>
       <x:c r="C3" s="3" t="str">
-        <x:v>pun-IPAN Anaerobic Workstations</x:v>
+        <x:v>pun-IPAN Anaerobic and Hypoxic Workstations</x:v>
       </x:c>
       <x:c r="D3" s="3" t="str">
         <x:v>有效规划模板，资料齐备后进入开发</x:v>
@@ -13177,7 +13976,7 @@
         <x:v>来源与事实</x:v>
       </x:c>
       <x:c r="C10" s="3" t="str">
-        <x:v>适用条件、容量、气体/环境参数与维护资料由工程确认；地区支持不默认全球</x:v>
+        <x:v>厌氧与低氧版本及低氧版两类任务已有用户业务确认；发布时由研发提供对应型号的适用条件、配置、容量、气体与环境参数、测试和维护资料。氧浓度、温控、CO2等功能与数值按实际资料填写；地区支持另行确认。</x:v>
       </x:c>
       <x:c r="D10" s="8" t="str">
         <x:v>待检查</x:v>
@@ -13342,7 +14141,7 @@
         <x:v>适用范围</x:v>
       </x:c>
       <x:c r="C21" s="3" t="str">
-        <x:v>有效规划模板，资料齐备后进入开发</x:v>
+        <x:v>有效规划模板，覆盖厌氧与低氧版本；低氧版按微需氧微生物、细胞与组织培养分别准备资料。</x:v>
       </x:c>
       <x:c r="D21" s="8" t="str">
         <x:v>待检查</x:v>
